--- a/artfynd/A 51108-2025 artfynd.xlsx
+++ b/artfynd/A 51108-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56016149</v>
+        <v>56016154</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727097.9540847437</v>
+        <v>727098</v>
       </c>
       <c r="R2" t="n">
-        <v>7470203.817437783</v>
+        <v>7470204</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56016134</v>
+        <v>56016128</v>
       </c>
       <c r="B3" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>728024.922880529</v>
+        <v>727780</v>
       </c>
       <c r="R3" t="n">
-        <v>7471305.032591257</v>
+        <v>7471500</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +840,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56016148</v>
+        <v>56016112</v>
       </c>
       <c r="B4" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727274.0384769693</v>
+        <v>726981</v>
       </c>
       <c r="R4" t="n">
-        <v>7470151.164089461</v>
+        <v>7470274</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,19 +937,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56016118</v>
+        <v>56016137</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726981.09225746</v>
+        <v>728025</v>
       </c>
       <c r="R5" t="n">
-        <v>7470273.95395383</v>
+        <v>7471305</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1084,19 +1034,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56016123</v>
+        <v>56016148</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727656.1559069019</v>
+        <v>727274</v>
       </c>
       <c r="R6" t="n">
-        <v>7470612.0859405</v>
+        <v>7470151</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1196,19 +1131,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56016115</v>
+        <v>56016149</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726981.09225746</v>
+        <v>727098</v>
       </c>
       <c r="R7" t="n">
-        <v>7470273.95395383</v>
+        <v>7470204</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1308,19 +1228,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56016112</v>
+        <v>56016113</v>
       </c>
       <c r="B8" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726981.09225746</v>
+        <v>726981</v>
       </c>
       <c r="R8" t="n">
-        <v>7470273.95395383</v>
+        <v>7470274</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1420,19 +1325,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56016125</v>
+        <v>56016114</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727543.8968800213</v>
+        <v>726981</v>
       </c>
       <c r="R9" t="n">
-        <v>7470787.90698216</v>
+        <v>7470274</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1532,19 +1422,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56016128</v>
+        <v>56016136</v>
       </c>
       <c r="B10" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>727779.9321226076</v>
+        <v>728025</v>
       </c>
       <c r="R10" t="n">
-        <v>7471500.15334363</v>
+        <v>7471305</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1644,19 +1519,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56016136</v>
+        <v>56016117</v>
       </c>
       <c r="B11" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>728024.922880529</v>
+        <v>726981</v>
       </c>
       <c r="R11" t="n">
-        <v>7471305.032591257</v>
+        <v>7470274</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1756,19 +1616,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>56016117</v>
+        <v>56016121</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726981.09225746</v>
+        <v>727656</v>
       </c>
       <c r="R12" t="n">
-        <v>7470273.95395383</v>
+        <v>7470612</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1868,19 +1713,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56016119</v>
+        <v>56016129</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727391.9764963663</v>
+        <v>728025</v>
       </c>
       <c r="R13" t="n">
-        <v>7470392.886618953</v>
+        <v>7471305</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1980,19 +1810,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>56016129</v>
+        <v>56016153</v>
       </c>
       <c r="B14" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>728024.922880529</v>
+        <v>727098</v>
       </c>
       <c r="R14" t="n">
-        <v>7471305.032591257</v>
+        <v>7470204</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2092,19 +1907,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>56016133</v>
+        <v>56016151</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>728024.922880529</v>
+        <v>727098</v>
       </c>
       <c r="R15" t="n">
-        <v>7471305.032591257</v>
+        <v>7470204</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2204,19 +2004,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>56016121</v>
+        <v>56016122</v>
       </c>
       <c r="B16" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>4217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>727656.1559069019</v>
+        <v>727656</v>
       </c>
       <c r="R16" t="n">
-        <v>7470612.0859405</v>
+        <v>7470612</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2316,19 +2101,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>56016120</v>
+        <v>56016134</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727620.9571167078</v>
+        <v>728025</v>
       </c>
       <c r="R17" t="n">
-        <v>7470513.85511224</v>
+        <v>7471305</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2428,19 +2198,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>56016154</v>
+        <v>56016152</v>
       </c>
       <c r="B18" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>4217</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>727097.9540847437</v>
+        <v>727098</v>
       </c>
       <c r="R18" t="n">
-        <v>7470203.817437783</v>
+        <v>7470204</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2540,19 +2295,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>56016147</v>
+        <v>56016118</v>
       </c>
       <c r="B19" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>727274.0384769693</v>
+        <v>726981</v>
       </c>
       <c r="R19" t="n">
-        <v>7470151.164089461</v>
+        <v>7470274</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2652,19 +2392,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>56016152</v>
+        <v>56016125</v>
       </c>
       <c r="B20" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>727097.9540847437</v>
+        <v>727544</v>
       </c>
       <c r="R20" t="n">
-        <v>7470203.817437783</v>
+        <v>7470788</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2764,19 +2489,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>56016114</v>
+        <v>56016116</v>
       </c>
       <c r="B21" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>726981.09225746</v>
+        <v>726981</v>
       </c>
       <c r="R21" t="n">
-        <v>7470273.95395383</v>
+        <v>7470274</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2876,19 +2586,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>56016151</v>
+        <v>56016126</v>
       </c>
       <c r="B22" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>727097.9540847437</v>
+        <v>727282</v>
       </c>
       <c r="R22" t="n">
-        <v>7470203.817437783</v>
+        <v>7471550</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2988,19 +2683,9 @@
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,566 +2709,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>56016122</v>
-      </c>
-      <c r="B23" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>4217</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Blodticka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Meruliopsis taxicola</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Latnivaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>727656.1559069019</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7470612.0859405</v>
-      </c>
-      <c r="S23" t="n">
-        <v>50</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Sture Westerberg, Camilla Carlsson, Robert Sandberg</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>56016124</v>
-      </c>
-      <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Latnivaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>727543.8968800213</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7470787.90698216</v>
-      </c>
-      <c r="S24" t="n">
-        <v>50</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Sture Westerberg, Camilla Carlsson, Robert Sandberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>56016137</v>
-      </c>
-      <c r="B25" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>864</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Latnivaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>728024.922880529</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7471305.032591257</v>
-      </c>
-      <c r="S25" t="n">
-        <v>50</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Sture Westerberg, Camilla Carlsson, Robert Sandberg</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>56016113</v>
-      </c>
-      <c r="B26" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>918</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tajgaskinn</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Laurilia sulcata</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Burt) Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Latnivaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>726981.09225746</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7470273.95395383</v>
-      </c>
-      <c r="S26" t="n">
-        <v>50</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Sture Westerberg, Camilla Carlsson, Robert Sandberg</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>56016153</v>
-      </c>
-      <c r="B27" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Latnivaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>727097.9540847437</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7470203.817437783</v>
-      </c>
-      <c r="S27" t="n">
-        <v>50</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Sture Westerberg, Camilla Carlsson, Robert Sandberg</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51108-2025 artfynd.xlsx
+++ b/artfynd/A 51108-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016112</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016137</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016148</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016149</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016113</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016114</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016136</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016117</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016121</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016129</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016153</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016151</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016122</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016134</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016152</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016118</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016125</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016116</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,8 +2814,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56016126</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>